--- a/data/601238_广汽集团_财务数据.xlsx
+++ b/data/601238_广汽集团_财务数据.xlsx
@@ -12522,7 +12522,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -20540,7 +20540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -20570,8 +20570,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20618,22 +20616,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -20643,75 +20641,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -20745,58 +20733,52 @@
         <v>5.562570325242569</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>0.6201736481163902</v>
+      <c r="J2" s="3" t="n">
+        <v>45.37957413633485</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>45.37957413633485</v>
+        <v>1.437834059699038</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.437834059699038</v>
+        <v>1.335293150234356</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.335293150234356</v>
+        <v>83.08169227681259</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>15.3423396929525</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>23.46447850880045</v>
-      </c>
-      <c r="P2" s="3" t="n">
         <v>19.44089600721732</v>
       </c>
+      <c r="P2" s="6" t="n">
+        <v>0.60197919591434</v>
+      </c>
       <c r="Q2" s="3" t="n">
-        <v>18.51766502255617</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0.60197919591434</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.413104462297332</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>0.8732007748063897</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>286000000</v>
       </c>
+      <c r="X2" s="3" t="n">
+        <v>1.174316651853037</v>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
       <c r="Z2" s="3" t="n">
-        <v>1.174316651853037</v>
+        <v>2.255407037647285</v>
       </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>2.255407037647285</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -20832,64 +20814,58 @@
       <c r="I3" s="6" t="n">
         <v>0.6966651502358292</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>0.4435329657972517</v>
+      <c r="J3" s="3" t="n">
+        <v>41.12640256851892</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>41.12640256851892</v>
+        <v>1.75521924929911</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.75521924929911</v>
+        <v>1.664117150711778</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.664117150711778</v>
+        <v>69.85542647768909</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>20.13782154394904</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>17.87680952551552</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>23.43399692347201</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.7053938600454154</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>15.36229611942195</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.7053938600454154</v>
-      </c>
+        <v>1.430519116071429</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.430519116071429</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>43.95022215661288</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>71.88041533177038</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>43.95022215661288</v>
+        <v>45.69263752862642</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>71.88041533177038</v>
+        <v>1.498119183254447</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>45.69263752862642</v>
+        <v>10004000000</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>1.498119183254447</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>10004000000</v>
+        <v>1.141096277757488</v>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>+/+/+</t>
+        </is>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>1.141096277757488</v>
+        <v>2.509901952676902</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>+/+/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.509901952676902</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -20925,64 +20901,58 @@
       <c r="I4" s="3" t="n">
         <v>1.172337038935685</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>-0.2108958689374823</v>
+      <c r="J4" s="3" t="n">
+        <v>41.02255525280049</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>41.02255525280049</v>
+        <v>1.647467330429371</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.647467330429371</v>
+        <v>1.479950217797138</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.479950217797138</v>
+        <v>69.55634552944649</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>13.29389699340087</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>27.08009548883258</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>13.98917258846879</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0.5682023730623466</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>25.73418818899599</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0.5682023730623466</v>
-      </c>
-      <c r="S4" s="3" t="n">
         <v>1.094565306660953</v>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="6" t="n">
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="6" t="n">
         <v>0.5308981878695042</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>1.146600730949527</v>
       </c>
+      <c r="U4" s="3" t="n">
+        <v>10.46638016086688</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>-0.1158379715973974</v>
+      </c>
       <c r="W4" s="3" t="n">
-        <v>10.46638016086688</v>
-      </c>
-      <c r="X4" s="6" t="n">
-        <v>-0.1158379715973974</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>-11120000000</v>
       </c>
+      <c r="X4" s="3" t="n">
+        <v>1.096644446926699</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
+      </c>
       <c r="Z4" s="3" t="n">
-        <v>1.096644446926699</v>
+        <v>2.403800735934657</v>
       </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.403800735934657</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21018,64 +20988,58 @@
       <c r="I5" s="3" t="n">
         <v>1.692368114695092</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.04439183775852004</v>
+      <c r="J5" s="3" t="n">
+        <v>39.99345025835092</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>39.99345025835092</v>
+        <v>1.367440182758206</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.367440182758206</v>
+        <v>1.200841649633281</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.200841649633281</v>
+        <v>66.6492832367138</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>9.385784222151798</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>38.35587857968738</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>9.584520113486601</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>37.56056596860135</v>
-      </c>
-      <c r="R5" s="6" t="n">
+      <c r="P5" s="6" t="n">
         <v>0.439533144555337</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0.9627423239931086</v>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
+        <v>-17.17250544787123</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-38.69041878487212</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>-17.17250544787123</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-38.69041878487212</v>
+        <v>4.003935815924905</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>-0.05677123168955062</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>4.003935815924905</v>
-      </c>
-      <c r="X5" s="6" t="n">
-        <v>-0.05677123168955062</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>-10482000000</v>
       </c>
+      <c r="X5" s="3" t="n">
+        <v>1.136144085571842</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
+      </c>
       <c r="Z5" s="3" t="n">
-        <v>1.136144085571842</v>
+        <v>2.099606250293967</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>2.099606250293967</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21111,64 +21075,58 @@
       <c r="I6" s="3" t="n">
         <v>1.556806471876332</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>0.05555498368964869</v>
+      <c r="J6" s="3" t="n">
+        <v>39.31670016175678</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>39.31670016175678</v>
+        <v>1.336392591718768</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.336392591718768</v>
+        <v>1.18015807479061</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.18015807479061</v>
+        <v>64.78998384491115</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>10.53272506238979</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>34.1791889437508</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>10.05981105476015</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0.4476324518783657</v>
+      </c>
       <c r="Q6" s="3" t="n">
-        <v>35.78596039630919</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0.4476324518783657</v>
-      </c>
+        <v>1.105069446805512</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>1.105069446805512</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>5.880821366284332</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-9.835535665460991</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>5.880821366284332</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-9.835535665460991</v>
+        <v>3.92766174223129</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>-0.4771058239423291</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>3.92766174223129</v>
-      </c>
-      <c r="X6" s="6" t="n">
-        <v>-0.4771058239423291</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>-9473000000</v>
       </c>
+      <c r="X6" s="3" t="n">
+        <v>1.134730194512046</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>−/+/−</t>
+        </is>
+      </c>
       <c r="Z6" s="3" t="n">
-        <v>1.134730194512046</v>
+        <v>2.120035919172594</v>
       </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>−/+/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2.120035919172594</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21204,64 +21162,58 @@
       <c r="I7" s="3" t="n">
         <v>1.316330272783922</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>0.2289221577470127</v>
+      <c r="J7" s="3" t="n">
+        <v>39.95019358353276</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>39.95019358353276</v>
+        <v>1.253780272917264</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.253780272917264</v>
+        <v>1.087591689546367</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.087591689546367</v>
+        <v>66.52843026081322</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>9.88551684127402</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>36.41691231529015</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>10.93085925419127</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.5057854908351402</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>32.93428189206293</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.5057854908351402</v>
-      </c>
+        <v>1.274836117622099</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.274836117622099</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>19.76023018681571</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>22.14367970561777</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>19.76023018681571</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>22.14367970561777</v>
+        <v>7.975799505626475</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>-0.756190199150746</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>7.975799505626475</v>
-      </c>
-      <c r="X7" s="6" t="n">
-        <v>-0.756190199150746</v>
-      </c>
-      <c r="Y7" s="3" t="n">
         <v>-11832000000</v>
       </c>
+      <c r="X7" s="3" t="n">
+        <v>1.18182418454102</v>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
+      </c>
       <c r="Z7" s="3" t="n">
-        <v>1.18182418454102</v>
+        <v>2.155306133997273</v>
       </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2.155306133997273</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21297,64 +21249,58 @@
       <c r="I8" s="3" t="n">
         <v>1.557287583300567</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.1643879206981572</v>
+      <c r="J8" s="3" t="n">
+        <v>35.58620253698007</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>35.58620253698007</v>
+        <v>1.6182560152634</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.6182560152634</v>
+        <v>1.399869271808642</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.399869271808642</v>
+        <v>55.24669398169729</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>12.7545874871407</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>28.22513863054808</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>11.15960655263029</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0.6371565785268103</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>32.25920181882656</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.6371565785268103</v>
-      </c>
+        <v>1.434604146431493</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>1.434604146431493</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>45.91924010406169</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>8.099400726776308</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>45.91924010406169</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>8.099400726776308</v>
+        <v>23.1100475365928</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>-0.6694933170153894</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>23.1100475365928</v>
-      </c>
-      <c r="X8" s="6" t="n">
-        <v>-0.6694933170153894</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>-13363000000</v>
       </c>
+      <c r="X8" s="3" t="n">
+        <v>1.181010938877741</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
       <c r="Z8" s="3" t="n">
-        <v>1.181010938877741</v>
+        <v>2.47143474242551</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>2.47143474242551</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21390,64 +21336,58 @@
       <c r="I9" s="3" t="n">
         <v>1.346520549061548</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.2383318929772057</v>
+      <c r="J9" s="3" t="n">
+        <v>43.03898898784313</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>43.03898898784313</v>
+        <v>1.310967624826585</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.310967624826585</v>
+        <v>1.094182322662621</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1.094182322662621</v>
+        <v>75.55868167202571</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>18.462475301692</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>19.49901051279986</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>9.271367731999176</v>
       </c>
+      <c r="P9" s="6" t="n">
+        <v>0.6308122821567412</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>38.82922244120432</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0.6308122821567412</v>
-      </c>
+        <v>1.336252713907656</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.336252713907656</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>17.47910831578351</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-53.18631275361479</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>17.47910831578351</v>
+        <v>15.04646213494035</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>-53.18631275361479</v>
+        <v>1.798816165073231</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>15.04646213494035</v>
+        <v>-4849000000</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1.798816165073231</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>-4849000000</v>
+        <v>1.25596759594264</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.25596759594264</v>
+        <v>1.980011228084817</v>
       </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>1.980011228084817</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -21483,64 +21423,58 @@
       <c r="I10" s="3" t="n">
         <v>1.696565697194202</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>0.1560272052310131</v>
+      <c r="J10" s="3" t="n">
+        <v>47.61376248612653</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>47.61376248612653</v>
+        <v>1.238458477049615</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.238458477049615</v>
+        <v>1.065026090032723</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.065026090032723</v>
+        <v>90.88908414561043</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>23.24471851735771</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>15.48738909146929</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>7.123169598802765</v>
       </c>
+      <c r="P10" s="6" t="n">
+        <v>0.4737591154012505</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>50.5392992552792</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.4737591154012505</v>
-      </c>
+        <v>1.002152223480672</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.002152223480672</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>-17.05491110508511</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-113.2088723035377</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>-17.05491110508511</v>
+        <v>6.439249982829293</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-113.2088723035377</v>
+        <v>-22.10130527062249</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>6.439249982829293</v>
+        <v>60000000</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-22.10130527062249</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>60000000</v>
+        <v>1.320213729181512</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1.320213729181512</v>
+        <v>1.604905564669109</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.604905564669109</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -21576,64 +21510,58 @@
       <c r="I11" s="3" t="n">
         <v>1.713146392889225</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.2852041084317004</v>
+      <c r="J11" s="3" t="n">
+        <v>48.97112257668311</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>48.97112257668311</v>
-      </c>
-      <c r="L11" s="3" t="n">
         <v>1.143387824321362</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.9536576643093643</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>95.96659494547974</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>22.38481935883936</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>16.08232768060478</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>6.887349854359868</v>
       </c>
-      <c r="Q11" s="3" t="n">
-        <v>52.26974200709593</v>
-      </c>
-      <c r="R11" s="6" t="n">
+      <c r="P11" s="6" t="n">
         <v>0.4276321489223314</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>0.9061602524439224</v>
       </c>
-      <c r="T11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="3" t="n">
+        <v>-10.42748775911821</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-2224.033014204775</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>-10.42748775911821</v>
+        <v>-7.534694439425629</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-2224.033014204775</v>
+        <v>1.308688085628088</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-7.534694439425629</v>
+        <v>-23987000000</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.308688085628088</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>-23987000000</v>
+        <v>1.130402211347632</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.130402211347632</v>
+        <v>1.318474877732318</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.318474877732318</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>

--- a/data/601238_广汽集团_财务数据.xlsx
+++ b/data/601238_广汽集团_财务数据.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务分析指标" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量校验" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并报表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43020,4 +43021,2123 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>营业利润率</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>净利润率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>净资产收益率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>存货周转率</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总资产周转率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>应收账款周转率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>流动比率</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>速动比率</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>利息保障倍数</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>货币资金占比</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>营业收入增长率</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>营业利润增长率</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>净利润增长率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2016Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.06980232249447105</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.200593833918339</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1855492606155987</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.04549539606426556</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.265930994575045</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1286209926588056</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.702857667144906</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.620377823019743</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.495289048813977</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.448947758037225</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2470521362098139</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.7947224863426784</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.7030709809710692</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.7010543056013461</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.05334774347695659</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2028766053501348</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1873202702425848</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.09623027268662308</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10.52993066649364</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2776420285945648</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22.18333941200828</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.524328859060403</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.398710702931826</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.4562800919750499</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2681885742596898</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.112420398919861</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.136459886297923</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.13258279056894</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2016Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.04219273904457299</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1787013023469314</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1638491427396217</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.132102790008597</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14.09944953339041</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4263070361132117</v>
+      </c>
+      <c r="H4" t="n">
+        <v>35.19672922620266</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.451492086504772</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.290282308404817</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4658693362708664</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2165865704705298</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6046961856178747</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4134764220160334</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4036286304228083</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017年报</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.03792501937312676</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1659692118343411</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1521326250541231</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1918488133042821</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22.4537362253937</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7035903546691328</v>
+      </c>
+      <c r="H5" t="n">
+        <v>61.00930926586621</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.75521924929911</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.63118212254008</v>
+      </c>
+      <c r="K5" t="n">
+        <v>19.89285228275199</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4112640256851892</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4136051236601395</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.068701301356447</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9213107011399515</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.9207726947242216</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1100293358551007</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2489116385783491</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2269583402684389</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06529176286708278</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.336256036221591</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1652819726303631</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13.09399804420318</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.530261040586447</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.369435008045772</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.422171593162716</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2244782321276797</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.7626446857681197</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.6440273497851741</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.6459025922099452</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.05781560623256166</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1977646179965749</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1788323951724867</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1268291181496487</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.36789281949521</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3977488875487029</v>
+      </c>
+      <c r="H7" t="n">
+        <v>26.74232113503086</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.512469551096161</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.345628890693268</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21.20237361401756</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4347971728134526</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2648645027300439</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.052629107034902</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6308494595106393</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.617374268677009</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.05436331305807951</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1942677618894843</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1746839281598599</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1768338861506284</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15.33184525571857</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5665700114112459</v>
+      </c>
+      <c r="H8" t="n">
+        <v>39.03372581466008</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.412344763670065</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.236404077849861</v>
+      </c>
+      <c r="K8" t="n">
+        <v>22.24918531249866</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.424897376988491</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2778715388551954</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4827118870572868</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.4564947094355447</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.448316657117241</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018年报</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01440368760343691</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1628326923822455</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1530643629160112</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1699250386602558</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14.67050600208138</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.638633680649756</v>
+      </c>
+      <c r="H9" t="n">
+        <v>42.00559111659324</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.647467330429371</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.444455507156192</v>
+      </c>
+      <c r="K9" t="n">
+        <v>27.57065487951278</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4102255525280049</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3171964880411747</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.391660659947028</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1664717292133149</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.2194233010098716</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2018Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.08029895944707044</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2229441438213338</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2031124048843442</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0517695820196535</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.468239502209999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1532027547076452</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.7338233306846</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.897386931474585</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.739870778828098</v>
+      </c>
+      <c r="K10" t="n">
+        <v>45.44348430524041</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3721293350100858</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3717579737177485</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.731571500854461</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.6324782140261842</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.6438024046729796</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.05217235681568</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2040806526568649</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1892028813159574</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.09422311287387811</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.26171921394281</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3075795783488914</v>
+      </c>
+      <c r="H11" t="n">
+        <v>65.9585475669362</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.869436563863214</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.629633019126933</v>
+      </c>
+      <c r="K11" t="n">
+        <v>41.5644900088607</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3778672634845623</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3388882880034611</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9121123567495635</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.7503269250769431</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7811672679611352</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2018Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0353387262171504</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.20037300180142</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1873072197616642</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1323419431995866</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7.375270435518888</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4342092238105416</v>
+      </c>
+      <c r="H12" t="n">
+        <v>57.44689558999456</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.805531047491557</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.510176762298823</v>
+      </c>
+      <c r="K12" t="n">
+        <v>39.38264343805397</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.374458821713738</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3226356702487999</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4390704177324976</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4129259959272498</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4246520830547047</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019年报</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.1049909981164101</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.09592026100085251</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1132994791172252</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.08497367577284838</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.956919309613411</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4547325108225441</v>
+      </c>
+      <c r="H13" t="n">
+        <v>22.33126643770028</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.367440182758206</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.16996513165805</v>
+      </c>
+      <c r="K13" t="n">
+        <v>12.3917998119375</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3999345025835092</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.23464813332363</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1213739103759335</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.4631887669706816</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.3216968352693336</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.0328672910163188</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.1646283743255871</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1975884848190806</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.03480486251417331</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.970506061826698</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1082085895662866</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.504280834439179</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.765110916236318</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.466660170840235</v>
+      </c>
+      <c r="K14" t="n">
+        <v>22.29330985194784</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3581320093272632</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.247227994479783</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.7593253057397625</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.5869289423949915</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.5802756681345947</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.07240066386750543</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1595705360180341</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1768781558435145</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.062218500445878</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.89224229941279</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.220475959766533</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9.754742034686091</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.576471254281428</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.316160443853143</v>
+      </c>
+      <c r="K15" t="n">
+        <v>22.09908609517597</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3716218834525572</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2412403413186183</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9727009636161781</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.9120941420764608</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.7659313942036901</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.08500747057828351</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.1378550491515702</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1504206215123239</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.08012372812415022</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.966356799638989</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3351778247072958</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12.24964570038743</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.538061327350177</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.286671219068058</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20.04463303028843</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3474634942107985</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2085226594517169</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5177616154780003</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.3112138827335875</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.2907339768384434</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020年报</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.08670852964996945</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.08989444725029717</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.09648193801450669</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.07282770361463432</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10.95919277954655</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.4672152878810453</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14.96114298282443</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.336392591718768</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.152837088592662</v>
+      </c>
+      <c r="K17" t="n">
+        <v>14.29743066010361</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3931670016175678</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1995700490872296</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4693391519161623</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.04185278887030597</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.05754485287877686</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.1110266705132703</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.00143136667696402</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.01037095612841251</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.001441741104182509</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.832637992185704</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.07970104171818201</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.677641787837334</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.440533708763959</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.188813873868109</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.148111792993731</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3531125578181076</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1589929243986524</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.8283489374680222</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.9972668432980111</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.9815490269417384</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.09513606344435188</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.08806260160596101</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.09210323993715293</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02884430696869964</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.196618323717708</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1978724601168299</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.56492312</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.457737556561086</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.217737556561086</v>
+      </c>
+      <c r="K19" t="n">
+        <v>12.18653094884156</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3606986832271337</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1691694853875966</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.363027674314798</v>
+      </c>
+      <c r="O19" t="n">
+        <v>144.3815909061263</v>
+      </c>
+      <c r="P19" t="n">
+        <v>19.98577047002349</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.08873768059720399</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.1157428431346226</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1183021873306367</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.06109362452823275</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.993204244809235</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3271743989676079</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.809089958791208</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.378471591940461</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.134688691232529</v>
+      </c>
+      <c r="K20" t="n">
+        <v>17.1662129835782</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3531473030144783</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.1741328550129041</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.6842633397593907</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.213668730835805</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.163355352865978</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021年报</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.07205440588923517</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.09513212445828445</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.09840210657442887</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.08463721874386994</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11.02590369656306</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5246478277208496</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12.5897011330875</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.253780272917264</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.072019833627013</v>
+      </c>
+      <c r="K21" t="n">
+        <v>16.89986838473573</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3995019358353276</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1558785190373354</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.7530218222912284</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4408553104430484</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.4581390596125379</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.08599455776194076</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1434115500484792</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1478521395455301</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0267210131182905</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.26976807550148</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1076542703501076</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.656662960708911</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.346769574822047</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.106635394223689</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20.34180011956627</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.367764081760025</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1454346870168371</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.7884506994644949</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.6810897131307956</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.6821407814082019</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.0842100224270006</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1228493689115089</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1268365274541703</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.04970162272065649</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.782607080115005</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.243210694660005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.16830184229765</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.340430534510685</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.142536182663671</v>
+      </c>
+      <c r="K23" t="n">
+        <v>21.12776561977915</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.3625541738662437</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1586125825000708</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.159806321617812</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8501358049065257</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.8528127807254986</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.07559871155773878</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.09424130131457199</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.09595641651202079</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.06024561002947498</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9.833106286946425</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.3873651279386029</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10.85301210180171</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.252677300981053</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.052247934296912</v>
+      </c>
+      <c r="K24" t="n">
+        <v>16.98130331763718</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.3723301851257655</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1637253944559925</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.6060559578899236</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.2320519413054007</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.2150393702049507</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022年报</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.04229137771670688</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.06794825778261414</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.07289791766570505</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.08024638912689765</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.25372083411102</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.6578760138357833</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16.33872544379845</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.6182560152634</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.377981132742112</v>
+      </c>
+      <c r="K25" t="n">
+        <v>23.70011353622172</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.3558620253698007</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.20820514981668</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.9884994940134553</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4337140333919813</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.5106595021160434</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.06270504144515221</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1232963501198498</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1293832673117888</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.02858647060723821</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.315427925256519</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1337528016226852</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.854468050317568</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.262912016610433</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.05448135651873</v>
+      </c>
+      <c r="K26" t="n">
+        <v>37.91774631749769</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.3553733817139273</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1304164186841246</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7888191767631116</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.6167992297357213</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.6251845624825546</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.06135573971399277</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.118402480573148</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1200250336101449</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.05869426279286957</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.596839778938776</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.3084066987157248</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.927132287496941</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.380122190704778</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.15409120663321</v>
+      </c>
+      <c r="K27" t="n">
+        <v>47.99414484473363</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.3525493275246321</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1554798510676021</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.0932135929873</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.010129914942449</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9418123925258235</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.05414007441689894</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.09800918040269886</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1006025890763602</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.08097844997212722</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.047100041903308</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.4826556634439556</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10.12220741387166</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.238537299527517</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.020629533506355</v>
+      </c>
+      <c r="K28" t="n">
+        <v>41.72317702140951</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.4010226316335589</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2019726299041931</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.6507375871557115</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.3664193283274089</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.383615318892039</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年报</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.04704708243674216</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.02549582146242976</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.02904874209073788</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.04098293667817188</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.567451436448797</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.657144621054485</v>
+      </c>
+      <c r="H29" t="n">
+        <v>19.99181783308749</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.310967624826585</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.066850778585969</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8.442681060876737</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.4303898898784313</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.223883330662332</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.6099581109911896</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.5811902069666552</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.5351286843365735</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.06803359585667379</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.04337361481187744</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0494913867162499</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.01333945535923391</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.826566338635995</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1270907973053337</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.057010580431943</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.492348214583403</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.222418564331677</v>
+      </c>
+      <c r="K30" t="n">
+        <v>12.23321038885804</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.372207327971403</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.175867251604517</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.7950183658209625</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.6512842523041638</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.6507654171325283</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.0548201146157683</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.03873311978138562</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.04262735924622703</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.02587378831995813</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.948119081194303</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3088120144408676</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7.765918326461131</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.591237210470152</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.374850919590735</v>
+      </c>
+      <c r="K31" t="n">
+        <v>14.41402424627637</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.3907212614647095</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.219944137398229</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.33349334550178</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.083835475839474</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.009857992213513</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.03839075201351427</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.03958167855886301</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.04267026620329994</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0392392606507679</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.090099045753719</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.4739605306999025</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14.46437823105977</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.494560158249942</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.282857225971608</v>
+      </c>
+      <c r="K32" t="n">
+        <v>14.0544893153716</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.4079709938047792</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.2265585595873659</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.5856475229692448</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.6203856264629757</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.5872435709394654</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024年报</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.08076923089426935</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.007673627204927517</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.004625965563085678</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.007166535935712079</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8.059198448470884</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.4825713218019972</v>
+      </c>
+      <c r="H33" t="n">
+        <v>24.54558934222018</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.238458477049615</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.048366056425223</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.566311993688385</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.4761376248612653</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2220788271429678</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.09361008267178561</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-1.212016174844463</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-1.118560370769183</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.08029338109431117</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.04500332448476769</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0511637003743248</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.01054846372201573</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.389558492603417</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.09595652293114028</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.794259430207749</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.341474096024992</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.061106812840314</v>
+      </c>
+      <c r="K34" t="n">
+        <v>8.144735061260182</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.408940935042196</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.1859588347979159</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.8001229587624221</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-2.172213752851313</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-3.210662597921418</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.07881106059051457</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.02487971474103585</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.02654284905310266</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.01300000917336808</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.792745841085052</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2136812938196508</v>
+      </c>
+      <c r="H35" t="n">
+        <v>9.845781837721654</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.374030928537366</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.101968798964507</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.719286871670194</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.42316388099036</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.1921122592875142</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.145908158808325</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.1863475301626529</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.1132602983042641</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.08766980740602803</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.01342954385635107</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.006660905593117129</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.001043721506002625</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.535054204476982</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.3370432306015009</v>
+      </c>
+      <c r="H36" t="n">
+        <v>19.78889221007617</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.245154944627939</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.011207985234117</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-1.112337902613428</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.4527763083571678</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.191553172603624</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.6163322644545106</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-1.872461973855547</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-1.405617219127508</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025年报</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.1567769748277399</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.1273888829336966</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.1200245077672242</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.08020107051680059</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.495219235193989</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.4368016434822116</v>
+      </c>
+      <c r="H37" t="n">
+        <v>22.97898763631996</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.143387824321362</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9307460689193711</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-11.51739496842526</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.4897112257668312</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.1804013156976501</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.2920224795148607</v>
+      </c>
+      <c r="O37" t="n">
+        <v>11.25576253007177</v>
+      </c>
+      <c r="P37" t="n">
+        <v>22.28127308818213</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.1487266122383974</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.06491742865827395</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.0560371936189474</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.006693117864739382</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.276623448277812</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.09180517171684137</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.5359108566482</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.247272632252838</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9793569291472322</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-6.40919208721077</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.4349076611238317</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.1799669682068991</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.7945928028835607</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.8953244054142243</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.9040992286520134</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.160113429652327</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.0925053325170104</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.08253677876287001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.02259607214361065</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.684425293291261</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1980542586901331</v>
+      </c>
+      <c r="H39" t="n">
+        <v>10.68160928385054</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.286407951139942</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.033155039641895</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-11.32463692776322</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.4465253842790037</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.1863112507111924</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.145882153868135</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.057815848357545</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.16065436448122</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.1664057704914719</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.0954914844848247</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.08707261403871411</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.03889460997929812</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.83259641074052</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.3114422104046243</v>
+      </c>
+      <c r="H40" t="n">
+        <v>17.94767446228842</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.226715931863728</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.015480961923848</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-13.10092449150127</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.453151346349849</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.1784894015753209</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.5717007514442778</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.6224366081137027</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.6580740727481458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/601238_广汽集团_财务数据.xlsx
+++ b/data/601238_广汽集团_财务数据.xlsx
@@ -43029,7 +43029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43108,6 +43108,21 @@
           <t>净利润增长率</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>有息负债率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>经营现金流/营收</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>权益乘数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43160,6 +43175,15 @@
       <c r="P2" t="n">
         <v>-0.7010543056013461</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0.2017502115059222</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1352478635660198</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.849177442616539</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43212,6 +43236,15 @@
       <c r="P3" t="n">
         <v>1.13258279056894</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.1917501937319766</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1538561627206281</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.881471389645777</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43264,6 +43297,15 @@
       <c r="P4" t="n">
         <v>0.4036286304228083</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.1668341221900762</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1593906828725194</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.917794544399304</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43316,6 +43358,15 @@
       <c r="P5" t="n">
         <v>0.9207726947242216</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.09288306215615123</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2279128039924378</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.724117053481332</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43368,6 +43419,15 @@
       <c r="P6" t="n">
         <v>-0.6459025922099452</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0.1504509396543583</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2064589739067245</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.768296246816683</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43420,6 +43480,15 @@
       <c r="P7" t="n">
         <v>0.617374268677009</v>
       </c>
+      <c r="Q7" t="n">
+        <v>0.1366026864971695</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.122655493366874</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.806025529855412</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43472,6 +43541,15 @@
       <c r="P8" t="n">
         <v>0.448316657117241</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0.137607386679152</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.08754979279043816</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.773916906495664</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43524,6 +43602,15 @@
       <c r="P9" t="n">
         <v>0.2194233010098716</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.09640478353012413</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.01773066532403864</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.725930764206401</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43576,6 +43663,15 @@
       <c r="P10" t="n">
         <v>-0.6438024046729796</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0.08721082349366575</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.06459499081487595</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.615376225339823</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43628,6 +43724,15 @@
       <c r="P11" t="n">
         <v>0.7811672679611352</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0.0878004542693834</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.1030623613849227</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.637685306300414</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43680,6 +43785,15 @@
       <c r="P12" t="n">
         <v>0.4246520830547047</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0.09524737838211045</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.09878381094811661</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.628000158686079</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43732,6 +43846,15 @@
       <c r="P13" t="n">
         <v>-0.3216968352693336</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0.09957062804744923</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.006432150979269395</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.714752789078294</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43784,6 +43907,15 @@
       <c r="P14" t="n">
         <v>-0.5802756681345947</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.1072555955647912</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.4230484945207968</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.58599695585997</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43836,6 +43968,15 @@
       <c r="P15" t="n">
         <v>0.7659313942036901</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.1010935526122035</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.1196888461824072</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.641214480144496</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43888,6 +44029,15 @@
       <c r="P16" t="n">
         <v>0.2907339768384434</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0.1046194246608045</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.2134528953532672</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.580433388250978</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43940,6 +44090,15 @@
       <c r="P17" t="n">
         <v>-0.05754485287877686</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.1053799883759199</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.04603209453196394</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.693611318651344</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43992,6 +44151,15 @@
       <c r="P18" t="n">
         <v>-0.9815490269417384</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0.09146451597703767</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.6012748843727683</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.590663801933695</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44044,6 +44212,15 @@
       <c r="P19" t="n">
         <v>19.98577047002349</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.09493246627166049</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.2502449274192596</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.608683796279081</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44096,6 +44273,15 @@
       <c r="P20" t="n">
         <v>1.163355352865978</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.099357446132189</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.172010968332376</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.590631658781466</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44148,6 +44334,15 @@
       <c r="P21" t="n">
         <v>0.4581390596125379</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.1038411901658268</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.0744107085673703</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.708383651491818</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -44200,6 +44395,15 @@
       <c r="P22" t="n">
         <v>-0.6821407814082019</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.1069660562561171</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.3304697828132599</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.623989311464836</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -44252,6 +44456,15 @@
       <c r="P23" t="n">
         <v>0.8528127807254986</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0.1130215562416792</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.2206115139208661</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.610538321167883</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -44304,6 +44517,15 @@
       <c r="P24" t="n">
         <v>0.2150393702049507</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.1077272917509521</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-0.1326269043606475</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.634257834319392</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -44356,6 +44578,15 @@
       <c r="P25" t="n">
         <v>0.5106595021160434</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0.1017320578195457</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-0.04880466870152762</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.676220750551876</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -44408,6 +44639,15 @@
       <c r="P26" t="n">
         <v>-0.6251845624825546</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0.08172224675382853</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.1383857052127929</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.606896055283616</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -44460,6 +44700,15 @@
       <c r="P27" t="n">
         <v>0.9418123925258235</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.09177199159089182</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.1116652419782807</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.59995947520389</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -44512,6 +44761,15 @@
       <c r="P28" t="n">
         <v>0.383615318892039</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0.1144955440008301</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.02508266250978138</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.727587786563627</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -44564,6 +44822,15 @@
       <c r="P29" t="n">
         <v>-0.5351286843365735</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0.1265230431099613</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.05225334684786247</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.887270998963014</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -44616,6 +44883,15 @@
       <c r="P30" t="n">
         <v>-0.6507654171325283</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.09988118449914697</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.0279620842750159</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.714733487732251</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -44668,6 +44944,15 @@
       <c r="P31" t="n">
         <v>1.009857992213513</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0.1210950654701769</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.000427272591688207</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.764668868963347</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -44720,6 +45005,15 @@
       <c r="P32" t="n">
         <v>0.5872435709394654</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0.120330982765676</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.041185280157308</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.819789240347398</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -44772,6 +45066,15 @@
       <c r="P33" t="n">
         <v>-1.118560370769183</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0.1552022300802726</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1022398770811436</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.032792906238523</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -44824,6 +45127,15 @@
       <c r="P34" t="n">
         <v>-3.210662597921418</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0.1460879879130758</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.2875889360241076</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.815502537897561</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -44876,6 +45188,15 @@
       <c r="P35" t="n">
         <v>0.1132602983042641</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0.1537508380146566</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.05752333133220543</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.860388102324141</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -44928,6 +45249,15 @@
       <c r="P36" t="n">
         <v>-1.405617219127508</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0.161503770184609</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.01327658209846142</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.960020385210179</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -44980,6 +45310,15 @@
       <c r="P37" t="n">
         <v>22.28127308818213</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0.1803920109052167</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-0.1570746432983421</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.042563098677209</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -45032,6 +45371,15 @@
       <c r="P38" t="n">
         <v>-0.9040992286520134</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0.1155315115798956</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.5704960657356929</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.879717417955073</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -45084,6 +45432,15 @@
       <c r="P39" t="n">
         <v>2.16065436448122</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0.1240225512646294</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-0.255397446113307</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.91113407620417</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -45135,6 +45492,15 @@
       </c>
       <c r="P40" t="n">
         <v>0.6580740727481458</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1180128599542528</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-0.1633575965664479</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.92784251939985</v>
       </c>
     </row>
   </sheetData>
